--- a/src/public/templates/template-absensi.xlsx
+++ b/src/public/templates/template-absensi.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/A98D17813A983A49/Dokumen/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a98d17813a983a49/Dokumen/KULIAH/Semester 6 - TI/Magang/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="37" documentId="8_{8C06BD1F-5CBE-48DD-920E-10841E45CA60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C1AA8EEA-087D-4879-9FB1-9664061F1543}"/>
+  <xr:revisionPtr revIDLastSave="338" documentId="8_{8C06BD1F-5CBE-48DD-920E-10841E45CA60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF9DAAE1-FD9F-46C7-92E5-B0252C75E123}"/>
   <bookViews>
-    <workbookView xWindow="-78" yWindow="0" windowWidth="11676" windowHeight="13758" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,10 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="9">
-  <si>
-    <t>Badru Salam</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="13">
   <si>
     <t>name</t>
   </si>
@@ -48,14 +45,29 @@
   <si>
     <t>pulang_lembur</t>
   </si>
+  <si>
+    <t>jumbo</t>
+  </si>
+  <si>
+    <t>koda</t>
+  </si>
+  <si>
+    <t>adit</t>
+  </si>
+  <si>
+    <t>adit jarwo</t>
+  </si>
+  <si>
+    <t>kodi</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="167" formatCode="h:mm;@"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="165" formatCode="h:mm;@"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -101,13 +113,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -123,10 +138,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -416,10 +427,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H71"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="2" max="2" width="9.83984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.83984375" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.62890625" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="11.9453125" customWidth="1"/>
@@ -430,39 +441,39 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B2" s="2">
-        <v>45413</v>
+        <v>45778</v>
       </c>
       <c r="C2" s="3">
-        <v>0.33333333333333331</v>
+        <v>0.33958333333333335</v>
       </c>
       <c r="D2" s="3">
         <v>0.5</v>
@@ -478,10 +489,10 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B3" s="2">
-        <v>45414</v>
+        <v>45779</v>
       </c>
       <c r="C3" s="3">
         <v>0.34375</v>
@@ -490,7 +501,7 @@
         <v>0.5</v>
       </c>
       <c r="E3" s="3">
-        <v>0.54166666666666663</v>
+        <v>0.54236111111111107</v>
       </c>
       <c r="F3" s="3">
         <v>0.71875</v>
@@ -500,10 +511,10 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B4" s="2">
-        <v>45415</v>
+        <v>45780</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -514,10 +525,10 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B5" s="2">
-        <v>45416</v>
+        <v>45781</v>
       </c>
       <c r="C5" s="3">
         <v>0.33333333333333331</v>
@@ -532,7 +543,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="G5" s="3">
-        <v>0.75</v>
+        <v>0.78402777777777777</v>
       </c>
       <c r="H5" s="3">
         <v>0.83333333333333337</v>
@@ -540,17 +551,1503 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B6" s="2">
-        <v>45417</v>
-      </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
+        <v>45782</v>
+      </c>
+      <c r="C6" s="3">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D6" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0.54861111111111116</v>
+      </c>
+      <c r="F6" s="3">
+        <v>0.70902777777777781</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0.78819444444444442</v>
+      </c>
+      <c r="H6" s="3">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="2">
+        <v>45783</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D7" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0.7895833333333333</v>
+      </c>
+      <c r="H7" s="3">
+        <v>0.91666666666666696</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="2">
+        <v>45784</v>
+      </c>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2">
+        <v>45785</v>
+      </c>
+      <c r="C9" s="3">
+        <v>0.33402777777777776</v>
+      </c>
+      <c r="D9" s="3">
+        <v>0.50138888888888888</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0.78472222222222221</v>
+      </c>
+      <c r="H9" s="3">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="2">
+        <v>45786</v>
+      </c>
+      <c r="C10" s="3">
+        <v>0.34027777777777779</v>
+      </c>
+      <c r="D10" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0.54722222222222228</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="2">
+        <v>45787</v>
+      </c>
+      <c r="C11" s="3">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0.51388888888888884</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0.7104166666666667</v>
+      </c>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="2">
+        <v>45788</v>
+      </c>
+      <c r="C12" s="3">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D12" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0.54791666666666672</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0.78125</v>
+      </c>
+      <c r="H12" s="3">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="2">
+        <v>45789</v>
+      </c>
+      <c r="C13" s="3">
+        <v>0.33888888888888891</v>
+      </c>
+      <c r="D13" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0.78333333333333333</v>
+      </c>
+      <c r="H13" s="3">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="2">
+        <v>45790</v>
+      </c>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" s="2">
+        <v>45791</v>
+      </c>
+      <c r="C15" s="3">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D15" s="3">
+        <v>0.50347222222222221</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0.71180555555555558</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0.78402777777777777</v>
+      </c>
+      <c r="H15" s="3">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="2">
+        <v>45778</v>
+      </c>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="2">
+        <v>45779</v>
+      </c>
+      <c r="C17" s="3">
+        <v>0.34027777777777779</v>
+      </c>
+      <c r="D17" s="3">
+        <v>0.50347222222222221</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0.54236111111111107</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0.71875</v>
+      </c>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="2">
+        <v>45780</v>
+      </c>
+      <c r="C18" s="3">
+        <v>0.34027777777777779</v>
+      </c>
+      <c r="D18" s="3">
+        <v>0.50347222222222221</v>
+      </c>
+      <c r="E18" s="3">
+        <v>0.54236111111111107</v>
+      </c>
+      <c r="F18" s="3">
+        <v>0.71875</v>
+      </c>
+      <c r="G18" s="3">
+        <v>0.7895833333333333</v>
+      </c>
+      <c r="H18" s="3">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="2">
+        <v>45781</v>
+      </c>
+      <c r="C19" s="3">
+        <v>0.3347222222222222</v>
+      </c>
+      <c r="D19" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E19" s="3">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F19" s="3">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="G19" s="3">
+        <v>0.78888888888888886</v>
+      </c>
+      <c r="H19" s="3">
+        <v>0.91666666666666696</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="2">
+        <v>45782</v>
+      </c>
+      <c r="C20" s="3">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D20" s="3">
+        <v>0.50555555555555554</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0.54861111111111116</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0.70902777777777781</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0.78472222222222221</v>
+      </c>
+      <c r="H20" s="3">
+        <v>0.95833333333333304</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="2">
+        <v>45783</v>
+      </c>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="2">
+        <v>45784</v>
+      </c>
+      <c r="C22" s="3">
+        <v>0.33402777777777776</v>
+      </c>
+      <c r="D22" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E22" s="3">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F22" s="3">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="2">
+        <v>45785</v>
+      </c>
+      <c r="C23" s="3">
+        <v>0.33402777777777776</v>
+      </c>
+      <c r="D23" s="3">
+        <v>0.50138888888888888</v>
+      </c>
+      <c r="E23" s="3">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F23" s="3">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="G23" s="3">
+        <v>0.78541666666666665</v>
+      </c>
+      <c r="H23" s="3">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="2">
+        <v>45786</v>
+      </c>
+      <c r="C24" s="3">
+        <v>0.34097222222222223</v>
+      </c>
+      <c r="D24" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E24" s="3">
+        <v>0.54722222222222228</v>
+      </c>
+      <c r="F24" s="3">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="G24" s="3">
+        <v>0.78333333333333333</v>
+      </c>
+      <c r="H24" s="3">
+        <v>0.91666666666666696</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" s="2">
+        <v>45787</v>
+      </c>
+      <c r="C25" s="3">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D25" s="3">
+        <v>0.5131944444444444</v>
+      </c>
+      <c r="E25" s="3">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F25" s="3">
+        <v>0.7104166666666667</v>
+      </c>
+      <c r="G25" s="3">
+        <v>0.78819444444444442</v>
+      </c>
+      <c r="H25" s="3">
+        <v>0.95833333333333404</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" s="2">
+        <v>45788</v>
+      </c>
+      <c r="C26" s="3">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D26" s="3">
+        <v>0.50694444444444442</v>
+      </c>
+      <c r="E26" s="3">
+        <v>0.54791666666666672</v>
+      </c>
+      <c r="F26" s="3">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" s="2">
+        <v>45789</v>
+      </c>
+      <c r="C27" s="3">
+        <v>0.33958333333333335</v>
+      </c>
+      <c r="D27" s="3">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="E27" s="3">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F27" s="3">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="G27" s="3">
+        <v>0.78472222222222221</v>
+      </c>
+      <c r="H27" s="3">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" s="2">
+        <v>45790</v>
+      </c>
+      <c r="C28" s="3">
+        <v>0.33958333333333335</v>
+      </c>
+      <c r="D28" s="3">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="E28" s="3">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F28" s="3">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="G28" s="3">
+        <v>0.78888888888888886</v>
+      </c>
+      <c r="H28" s="3">
+        <v>0.91666666666666696</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" s="2">
+        <v>45791</v>
+      </c>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="3"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" t="s">
+        <v>10</v>
+      </c>
+      <c r="B30" s="2">
+        <v>45778</v>
+      </c>
+      <c r="C30" s="3">
+        <v>0.33541666666666664</v>
+      </c>
+      <c r="D30" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E30" s="3">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F30" s="3">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="G30" s="3">
+        <v>0.79097222222222219</v>
+      </c>
+      <c r="H30" s="3">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" t="s">
+        <v>10</v>
+      </c>
+      <c r="B31" s="2">
+        <v>45779</v>
+      </c>
+      <c r="C31" s="3">
+        <v>0.34027777777777779</v>
+      </c>
+      <c r="D31" s="3">
+        <v>0.50347222222222221</v>
+      </c>
+      <c r="E31" s="3">
+        <v>0.54236111111111107</v>
+      </c>
+      <c r="F31" s="3">
+        <v>0.71875</v>
+      </c>
+      <c r="G31" s="3">
+        <v>0.79027777777777775</v>
+      </c>
+      <c r="H31" s="3">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" t="s">
+        <v>10</v>
+      </c>
+      <c r="B32" s="2">
+        <v>45780</v>
+      </c>
+      <c r="C32" s="3">
+        <v>0.34027777777777779</v>
+      </c>
+      <c r="D32" s="3">
+        <v>0.50347222222222221</v>
+      </c>
+      <c r="E32" s="3">
+        <v>0.54236111111111107</v>
+      </c>
+      <c r="F32" s="3">
+        <v>0.71875</v>
+      </c>
+      <c r="G32" s="3">
+        <v>0.78194444444444444</v>
+      </c>
+      <c r="H32" s="3">
+        <v>0.91666666666666696</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" t="s">
+        <v>10</v>
+      </c>
+      <c r="B33" s="2">
+        <v>45781</v>
+      </c>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="3"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" t="s">
+        <v>10</v>
+      </c>
+      <c r="B34" s="2">
+        <v>45782</v>
+      </c>
+      <c r="C34" s="3">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D34" s="3">
+        <v>0.50555555555555554</v>
+      </c>
+      <c r="E34" s="3">
+        <v>0.54861111111111116</v>
+      </c>
+      <c r="F34" s="3">
+        <v>0.70902777777777781</v>
+      </c>
+      <c r="G34" s="3">
+        <v>0.78263888888888888</v>
+      </c>
+      <c r="H34" s="3">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" t="s">
+        <v>10</v>
+      </c>
+      <c r="B35" s="2">
+        <v>45783</v>
+      </c>
+      <c r="C35" s="3">
+        <v>0.33402777777777776</v>
+      </c>
+      <c r="D35" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E35" s="3">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F35" s="3">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="G35" s="3">
+        <v>0.78472222222222221</v>
+      </c>
+      <c r="H35" s="3">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" t="s">
+        <v>10</v>
+      </c>
+      <c r="B36" s="2">
+        <v>45784</v>
+      </c>
+      <c r="C36" s="3">
+        <v>0.33402777777777776</v>
+      </c>
+      <c r="D36" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E36" s="3">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F36" s="3">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="G36" s="3">
+        <v>0.78541666666666665</v>
+      </c>
+      <c r="H36" s="3">
+        <v>0.91666666666666696</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" t="s">
+        <v>10</v>
+      </c>
+      <c r="B37" s="2">
+        <v>45785</v>
+      </c>
+      <c r="C37" s="3"/>
+      <c r="D37" s="3"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
+      <c r="H37" s="3"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" t="s">
+        <v>10</v>
+      </c>
+      <c r="B38" s="2">
+        <v>45786</v>
+      </c>
+      <c r="C38" s="3">
+        <v>0.34097222222222223</v>
+      </c>
+      <c r="D38" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E38" s="3">
+        <v>0.54722222222222228</v>
+      </c>
+      <c r="F38" s="3">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="G38" s="3"/>
+      <c r="H38" s="3"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39" t="s">
+        <v>10</v>
+      </c>
+      <c r="B39" s="2">
+        <v>45787</v>
+      </c>
+      <c r="C39" s="3">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D39" s="3">
+        <v>0.5131944444444444</v>
+      </c>
+      <c r="E39" s="3">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F39" s="3">
+        <v>0.7104166666666667</v>
+      </c>
+      <c r="G39" s="3"/>
+      <c r="H39" s="3"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" t="s">
+        <v>10</v>
+      </c>
+      <c r="B40" s="2">
+        <v>45788</v>
+      </c>
+      <c r="C40" s="3">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D40" s="3">
+        <v>0.50694444444444442</v>
+      </c>
+      <c r="E40" s="3">
+        <v>0.54791666666666672</v>
+      </c>
+      <c r="F40" s="3">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="G40" s="3"/>
+      <c r="H40" s="3"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" t="s">
+        <v>10</v>
+      </c>
+      <c r="B41" s="2">
+        <v>45789</v>
+      </c>
+      <c r="C41" s="3">
+        <v>0.33958333333333335</v>
+      </c>
+      <c r="D41" s="3">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="E41" s="3">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F41" s="3">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="G41" s="3">
+        <v>0.78263888888888888</v>
+      </c>
+      <c r="H41" s="3">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" t="s">
+        <v>10</v>
+      </c>
+      <c r="B42" s="2">
+        <v>45790</v>
+      </c>
+      <c r="C42" s="3">
+        <v>0.33958333333333335</v>
+      </c>
+      <c r="D42" s="3">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F42" s="3">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="G42" s="3">
+        <v>0.78680555555555554</v>
+      </c>
+      <c r="H42" s="3">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43" t="s">
+        <v>10</v>
+      </c>
+      <c r="B43" s="2">
+        <v>45791</v>
+      </c>
+      <c r="C43" s="3">
+        <v>0.3347222222222222</v>
+      </c>
+      <c r="D43" s="3">
+        <v>0.50347222222222221</v>
+      </c>
+      <c r="E43" s="3">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F43" s="3">
+        <v>0.71180555555555558</v>
+      </c>
+      <c r="G43" s="3"/>
+      <c r="H43" s="3"/>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" t="s">
+        <v>11</v>
+      </c>
+      <c r="B44" s="2">
+        <v>45778</v>
+      </c>
+      <c r="C44" s="3">
+        <v>0.33541666666666664</v>
+      </c>
+      <c r="D44" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E44" s="3">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F44" s="3">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="G44" s="3"/>
+      <c r="H44" s="3"/>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45" t="s">
+        <v>11</v>
+      </c>
+      <c r="B45" s="2">
+        <v>45779</v>
+      </c>
+      <c r="C45" s="3">
+        <v>0.34027777777777779</v>
+      </c>
+      <c r="D45" s="3">
+        <v>0.50347222222222221</v>
+      </c>
+      <c r="E45" s="3">
+        <v>0.54236111111111107</v>
+      </c>
+      <c r="F45" s="3">
+        <v>0.71875</v>
+      </c>
+      <c r="G45" s="3">
+        <v>0.78611111111111109</v>
+      </c>
+      <c r="H45" s="3">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A46" t="s">
+        <v>11</v>
+      </c>
+      <c r="B46" s="2">
+        <v>45780</v>
+      </c>
+      <c r="C46" s="3">
+        <v>0.34027777777777779</v>
+      </c>
+      <c r="D46" s="3">
+        <v>0.50347222222222221</v>
+      </c>
+      <c r="E46" s="3">
+        <v>0.54236111111111107</v>
+      </c>
+      <c r="F46" s="3">
+        <v>0.71875</v>
+      </c>
+      <c r="G46" s="3">
+        <v>0.78541666666666665</v>
+      </c>
+      <c r="H46" s="3">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A47" t="s">
+        <v>11</v>
+      </c>
+      <c r="B47" s="2">
+        <v>45781</v>
+      </c>
+      <c r="C47" s="3">
+        <v>0.3347222222222222</v>
+      </c>
+      <c r="D47" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E47" s="3">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F47" s="3">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="G47" s="3">
+        <v>0.78472222222222221</v>
+      </c>
+      <c r="H47" s="3">
+        <v>0.91666666666666696</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A48" t="s">
+        <v>11</v>
+      </c>
+      <c r="B48" s="2">
+        <v>45782</v>
+      </c>
+      <c r="C48" s="3">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D48" s="3">
+        <v>0.50555555555555554</v>
+      </c>
+      <c r="E48" s="3">
+        <v>0.54861111111111116</v>
+      </c>
+      <c r="F48" s="3">
+        <v>0.70902777777777781</v>
+      </c>
+      <c r="G48" s="3">
+        <v>0.7895833333333333</v>
+      </c>
+      <c r="H48" s="3">
+        <v>0.95833333333333304</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A49" t="s">
+        <v>11</v>
+      </c>
+      <c r="B49" s="2">
+        <v>45783</v>
+      </c>
+      <c r="C49" s="3">
+        <v>0.33402777777777776</v>
+      </c>
+      <c r="D49" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E49" s="3">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F49" s="3">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="G49" s="3"/>
+      <c r="H49" s="3"/>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A50" t="s">
+        <v>11</v>
+      </c>
+      <c r="B50" s="2">
+        <v>45784</v>
+      </c>
+      <c r="C50" s="3">
+        <v>0.33402777777777776</v>
+      </c>
+      <c r="D50" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E50" s="3">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F50" s="3">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="G50" s="3"/>
+      <c r="H50" s="3"/>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A51" t="s">
+        <v>11</v>
+      </c>
+      <c r="B51" s="2">
+        <v>45785</v>
+      </c>
+      <c r="C51" s="3">
+        <v>0.33402777777777776</v>
+      </c>
+      <c r="D51" s="3">
+        <v>0.50138888888888888</v>
+      </c>
+      <c r="E51" s="3">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F51" s="3">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="G51" s="3">
+        <v>0.79097222222222219</v>
+      </c>
+      <c r="H51" s="3">
+        <v>0.92361111111111116</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A52" t="s">
+        <v>11</v>
+      </c>
+      <c r="B52" s="2">
+        <v>45786</v>
+      </c>
+      <c r="C52" s="3">
+        <v>0.34097222222222223</v>
+      </c>
+      <c r="D52" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E52" s="3">
+        <v>0.54722222222222228</v>
+      </c>
+      <c r="F52" s="3">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="G52" s="3">
+        <v>0.77777777777777779</v>
+      </c>
+      <c r="H52" s="3">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A53" t="s">
+        <v>11</v>
+      </c>
+      <c r="B53" s="2">
+        <v>45787</v>
+      </c>
+      <c r="C53" s="3">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D53" s="3">
+        <v>0.5131944444444444</v>
+      </c>
+      <c r="E53" s="3">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F53" s="3">
+        <v>0.7104166666666667</v>
+      </c>
+      <c r="G53" s="3">
+        <v>0.78125</v>
+      </c>
+      <c r="H53" s="3">
+        <v>0.91666666666666696</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A54" t="s">
+        <v>11</v>
+      </c>
+      <c r="B54" s="2">
+        <v>45788</v>
+      </c>
+      <c r="C54" s="3">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D54" s="3">
+        <v>0.50694444444444442</v>
+      </c>
+      <c r="E54" s="3">
+        <v>0.54791666666666672</v>
+      </c>
+      <c r="F54" s="3">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="G54" s="3">
+        <v>0.78472222222222221</v>
+      </c>
+      <c r="H54" s="3">
+        <v>0.95833333333333304</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A55" t="s">
+        <v>11</v>
+      </c>
+      <c r="B55" s="2">
+        <v>45789</v>
+      </c>
+      <c r="C55" s="3">
+        <v>0.33958333333333335</v>
+      </c>
+      <c r="D55" s="3">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="E55" s="3">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F55" s="3">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="G55" s="3">
+        <v>0.78541666666666665</v>
+      </c>
+      <c r="H55" s="3">
+        <v>0.93055555555555558</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A56" t="s">
+        <v>11</v>
+      </c>
+      <c r="B56" s="2">
+        <v>45790</v>
+      </c>
+      <c r="C56" s="3"/>
+      <c r="D56" s="3"/>
+      <c r="E56" s="3"/>
+      <c r="F56" s="3"/>
+      <c r="G56" s="3"/>
+      <c r="H56" s="3"/>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A57" t="s">
+        <v>11</v>
+      </c>
+      <c r="B57" s="2">
+        <v>45791</v>
+      </c>
+      <c r="C57" s="3"/>
+      <c r="D57" s="3"/>
+      <c r="E57" s="3"/>
+      <c r="F57" s="3"/>
+      <c r="G57" s="3"/>
+      <c r="H57" s="3"/>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A58" t="s">
+        <v>12</v>
+      </c>
+      <c r="B58" s="2">
+        <v>45778</v>
+      </c>
+      <c r="C58" s="3">
+        <v>0.33541666666666664</v>
+      </c>
+      <c r="D58" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E58" s="3">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F58" s="3">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="G58" s="3">
+        <v>0.78611111111111109</v>
+      </c>
+      <c r="H58" s="3">
+        <v>0.90277777777777779</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A59" t="s">
+        <v>12</v>
+      </c>
+      <c r="B59" s="2">
+        <v>45779</v>
+      </c>
+      <c r="C59" s="3"/>
+      <c r="D59" s="3"/>
+      <c r="E59" s="3"/>
+      <c r="F59" s="3"/>
+      <c r="G59" s="3"/>
+      <c r="H59" s="3"/>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A60" t="s">
+        <v>12</v>
+      </c>
+      <c r="B60" s="2">
+        <v>45780</v>
+      </c>
+      <c r="C60" s="3">
+        <v>0.34027777777777779</v>
+      </c>
+      <c r="D60" s="3">
+        <v>0.50347222222222221</v>
+      </c>
+      <c r="E60" s="3">
+        <v>0.54236111111111107</v>
+      </c>
+      <c r="F60" s="3">
+        <v>0.71875</v>
+      </c>
+      <c r="G60" s="3">
+        <v>0.78749999999999998</v>
+      </c>
+      <c r="H60" s="3">
+        <v>0.95138888888888884</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A61" t="s">
+        <v>12</v>
+      </c>
+      <c r="B61" s="2">
+        <v>45781</v>
+      </c>
+      <c r="C61" s="3">
+        <v>0.3347222222222222</v>
+      </c>
+      <c r="D61" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E61" s="3">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F61" s="3">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="G61" s="3">
+        <v>0.79097222222222219</v>
+      </c>
+      <c r="H61" s="3">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A62" t="s">
+        <v>12</v>
+      </c>
+      <c r="B62" s="2">
+        <v>45782</v>
+      </c>
+      <c r="C62" s="3">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D62" s="3">
+        <v>0.50555555555555554</v>
+      </c>
+      <c r="E62" s="3">
+        <v>0.54861111111111116</v>
+      </c>
+      <c r="F62" s="3">
+        <v>0.70902777777777781</v>
+      </c>
+      <c r="G62" s="3">
+        <v>0.7895833333333333</v>
+      </c>
+      <c r="H62" s="3">
+        <v>0.91666666666666696</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A63" t="s">
+        <v>12</v>
+      </c>
+      <c r="B63" s="2">
+        <v>45783</v>
+      </c>
+      <c r="C63" s="3">
+        <v>0.33402777777777776</v>
+      </c>
+      <c r="D63" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E63" s="3">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F63" s="3">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="G63" s="3">
+        <v>0.78749999999999998</v>
+      </c>
+      <c r="H63" s="3">
+        <v>0.95833333333333304</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A64" t="s">
+        <v>12</v>
+      </c>
+      <c r="B64" s="2">
+        <v>45784</v>
+      </c>
+      <c r="C64" s="3"/>
+      <c r="D64" s="3"/>
+      <c r="E64" s="3"/>
+      <c r="F64" s="3"/>
+      <c r="G64" s="3"/>
+      <c r="H64" s="3"/>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A65" t="s">
+        <v>12</v>
+      </c>
+      <c r="B65" s="2">
+        <v>45785</v>
+      </c>
+      <c r="C65" s="3">
+        <v>0.33402777777777776</v>
+      </c>
+      <c r="D65" s="3">
+        <v>0.50138888888888888</v>
+      </c>
+      <c r="E65" s="3">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F65" s="3">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="G65" s="3">
+        <v>0.78541666666666665</v>
+      </c>
+      <c r="H65" s="3">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A66" t="s">
+        <v>12</v>
+      </c>
+      <c r="B66" s="2">
+        <v>45786</v>
+      </c>
+      <c r="C66" s="3">
+        <v>0.34097222222222223</v>
+      </c>
+      <c r="D66" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E66" s="3">
+        <v>0.54722222222222228</v>
+      </c>
+      <c r="F66" s="3">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="G66" s="3">
+        <v>0.78263888888888888</v>
+      </c>
+      <c r="H66" s="3">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A67" t="s">
+        <v>12</v>
+      </c>
+      <c r="B67" s="2">
+        <v>45787</v>
+      </c>
+      <c r="C67" s="3"/>
+      <c r="D67" s="3"/>
+      <c r="E67" s="3"/>
+      <c r="F67" s="3"/>
+      <c r="G67" s="3"/>
+      <c r="H67" s="3"/>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A68" t="s">
+        <v>12</v>
+      </c>
+      <c r="B68" s="2">
+        <v>45788</v>
+      </c>
+      <c r="C68" s="3">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D68" s="3">
+        <v>0.50694444444444442</v>
+      </c>
+      <c r="E68" s="3">
+        <v>0.54791666666666672</v>
+      </c>
+      <c r="F68" s="3">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="G68" s="3">
+        <v>0.78333333333333333</v>
+      </c>
+      <c r="H68" s="3">
+        <v>0.95833333333333337</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A69" t="s">
+        <v>12</v>
+      </c>
+      <c r="B69" s="2">
+        <v>45789</v>
+      </c>
+      <c r="C69" s="3"/>
+      <c r="D69" s="3"/>
+      <c r="E69" s="3"/>
+      <c r="F69" s="3"/>
+      <c r="G69" s="3"/>
+      <c r="H69" s="3"/>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A70" t="s">
+        <v>12</v>
+      </c>
+      <c r="B70" s="2">
+        <v>45790</v>
+      </c>
+      <c r="C70" s="3"/>
+      <c r="D70" s="3"/>
+      <c r="E70" s="3"/>
+      <c r="F70" s="3"/>
+      <c r="G70" s="3"/>
+      <c r="H70" s="3"/>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A71" t="s">
+        <v>12</v>
+      </c>
+      <c r="B71" s="2">
+        <v>45791</v>
+      </c>
+      <c r="C71" s="3">
+        <v>0.3347222222222222</v>
+      </c>
+      <c r="D71" s="3">
+        <v>0.50347222222222221</v>
+      </c>
+      <c r="E71" s="3">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F71" s="3">
+        <v>0.71180555555555558</v>
+      </c>
+      <c r="G71" s="3">
+        <v>0.78472222222222221</v>
+      </c>
+      <c r="H71" s="3">
+        <v>0.97916666666666663</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
